--- a/Fase 2/Evidencias Grupales/Gantt CAPSTONE_TresStock.xlsx
+++ b/Fase 2/Evidencias Grupales/Gantt CAPSTONE_TresStock.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvill\Desktop\TRESSTOCK ARCHIVOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvill\Documents\GitHub\ProyectoCapstone\Fase 2\Evidencias Grupales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95139901-761D-48B0-86D5-13BA4CBF993E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2A200A-724C-466D-8674-7A13F6AAD3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gestión Proyecto Carta Gantt" sheetId="3" r:id="rId1"/>
@@ -1782,39 +1782,6 @@
     <xf numFmtId="0" fontId="13" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1851,6 +1818,12 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1858,6 +1831,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1869,6 +1848,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1876,6 +1861,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2172,106 +2172,106 @@
     </row>
     <row r="6" spans="1:353" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2"/>
-      <c r="I6" s="147" t="s">
+      <c r="I6" s="136" t="s">
         <v>181</v>
       </c>
-      <c r="J6" s="147"/>
-      <c r="K6" s="147"/>
-      <c r="L6" s="147"/>
-      <c r="M6" s="147"/>
-      <c r="N6" s="147"/>
-      <c r="O6" s="147"/>
-      <c r="P6" s="147"/>
-      <c r="Q6" s="147"/>
-      <c r="R6" s="147"/>
-      <c r="S6" s="147"/>
-      <c r="T6" s="147"/>
-      <c r="U6" s="147"/>
-      <c r="V6" s="147"/>
-      <c r="W6" s="147"/>
-      <c r="X6" s="147"/>
-      <c r="Y6" s="148" t="s">
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="136"/>
+      <c r="P6" s="136"/>
+      <c r="Q6" s="136"/>
+      <c r="R6" s="136"/>
+      <c r="S6" s="136"/>
+      <c r="T6" s="136"/>
+      <c r="U6" s="136"/>
+      <c r="V6" s="136"/>
+      <c r="W6" s="136"/>
+      <c r="X6" s="136"/>
+      <c r="Y6" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="Z6" s="149"/>
-      <c r="AA6" s="149"/>
-      <c r="AB6" s="149"/>
-      <c r="AC6" s="149"/>
-      <c r="AD6" s="149"/>
-      <c r="AE6" s="149"/>
-      <c r="AF6" s="149"/>
-      <c r="AG6" s="149"/>
-      <c r="AH6" s="149"/>
-      <c r="AI6" s="149"/>
-      <c r="AJ6" s="149"/>
-      <c r="AK6" s="149"/>
-      <c r="AL6" s="149"/>
-      <c r="AM6" s="149"/>
-      <c r="AN6" s="149"/>
-      <c r="AO6" s="149"/>
-      <c r="AP6" s="149"/>
-      <c r="AQ6" s="149"/>
-      <c r="AR6" s="149"/>
-      <c r="AS6" s="149"/>
-      <c r="AT6" s="150"/>
-      <c r="AU6" s="147" t="s">
+      <c r="Z6" s="138"/>
+      <c r="AA6" s="138"/>
+      <c r="AB6" s="138"/>
+      <c r="AC6" s="138"/>
+      <c r="AD6" s="138"/>
+      <c r="AE6" s="138"/>
+      <c r="AF6" s="138"/>
+      <c r="AG6" s="138"/>
+      <c r="AH6" s="138"/>
+      <c r="AI6" s="138"/>
+      <c r="AJ6" s="138"/>
+      <c r="AK6" s="138"/>
+      <c r="AL6" s="138"/>
+      <c r="AM6" s="138"/>
+      <c r="AN6" s="138"/>
+      <c r="AO6" s="138"/>
+      <c r="AP6" s="138"/>
+      <c r="AQ6" s="138"/>
+      <c r="AR6" s="138"/>
+      <c r="AS6" s="138"/>
+      <c r="AT6" s="139"/>
+      <c r="AU6" s="136" t="s">
         <v>183</v>
       </c>
-      <c r="AV6" s="147"/>
-      <c r="AW6" s="147"/>
-      <c r="AX6" s="147"/>
-      <c r="AY6" s="147"/>
-      <c r="AZ6" s="147"/>
-      <c r="BA6" s="147"/>
-      <c r="BB6" s="147"/>
-      <c r="BC6" s="147"/>
-      <c r="BD6" s="147"/>
-      <c r="BE6" s="147"/>
-      <c r="BF6" s="147"/>
-      <c r="BG6" s="147"/>
-      <c r="BH6" s="147"/>
-      <c r="BI6" s="147"/>
-      <c r="BJ6" s="147"/>
-      <c r="BK6" s="147"/>
-      <c r="BL6" s="147"/>
-      <c r="BM6" s="147"/>
-      <c r="BN6" s="147"/>
-      <c r="BO6" s="147"/>
-      <c r="BP6" s="147"/>
-      <c r="BQ6" s="147" t="s">
+      <c r="AV6" s="136"/>
+      <c r="AW6" s="136"/>
+      <c r="AX6" s="136"/>
+      <c r="AY6" s="136"/>
+      <c r="AZ6" s="136"/>
+      <c r="BA6" s="136"/>
+      <c r="BB6" s="136"/>
+      <c r="BC6" s="136"/>
+      <c r="BD6" s="136"/>
+      <c r="BE6" s="136"/>
+      <c r="BF6" s="136"/>
+      <c r="BG6" s="136"/>
+      <c r="BH6" s="136"/>
+      <c r="BI6" s="136"/>
+      <c r="BJ6" s="136"/>
+      <c r="BK6" s="136"/>
+      <c r="BL6" s="136"/>
+      <c r="BM6" s="136"/>
+      <c r="BN6" s="136"/>
+      <c r="BO6" s="136"/>
+      <c r="BP6" s="136"/>
+      <c r="BQ6" s="136" t="s">
         <v>184</v>
       </c>
-      <c r="BR6" s="147"/>
-      <c r="BS6" s="147"/>
-      <c r="BT6" s="147"/>
-      <c r="BU6" s="147"/>
-      <c r="BV6" s="147"/>
-      <c r="BW6" s="147"/>
-      <c r="BX6" s="147"/>
-      <c r="BY6" s="147"/>
-      <c r="BZ6" s="147"/>
-      <c r="CA6" s="147"/>
-      <c r="CB6" s="147"/>
-      <c r="CC6" s="147"/>
-      <c r="CD6" s="147"/>
-      <c r="CE6" s="147"/>
-      <c r="CF6" s="147"/>
-      <c r="CG6" s="147"/>
-      <c r="CH6" s="147"/>
-      <c r="CI6" s="147"/>
-      <c r="CJ6" s="147"/>
-      <c r="CK6" s="147"/>
-      <c r="CL6" s="147" t="s">
+      <c r="BR6" s="136"/>
+      <c r="BS6" s="136"/>
+      <c r="BT6" s="136"/>
+      <c r="BU6" s="136"/>
+      <c r="BV6" s="136"/>
+      <c r="BW6" s="136"/>
+      <c r="BX6" s="136"/>
+      <c r="BY6" s="136"/>
+      <c r="BZ6" s="136"/>
+      <c r="CA6" s="136"/>
+      <c r="CB6" s="136"/>
+      <c r="CC6" s="136"/>
+      <c r="CD6" s="136"/>
+      <c r="CE6" s="136"/>
+      <c r="CF6" s="136"/>
+      <c r="CG6" s="136"/>
+      <c r="CH6" s="136"/>
+      <c r="CI6" s="136"/>
+      <c r="CJ6" s="136"/>
+      <c r="CK6" s="136"/>
+      <c r="CL6" s="136" t="s">
         <v>185</v>
       </c>
-      <c r="CM6" s="147"/>
-      <c r="CN6" s="147"/>
-      <c r="CO6" s="147"/>
-      <c r="CP6" s="147"/>
-      <c r="CQ6" s="147"/>
-      <c r="CR6" s="147"/>
-      <c r="CS6" s="147"/>
-      <c r="CT6" s="147"/>
+      <c r="CM6" s="136"/>
+      <c r="CN6" s="136"/>
+      <c r="CO6" s="136"/>
+      <c r="CP6" s="136"/>
+      <c r="CQ6" s="136"/>
+      <c r="CR6" s="136"/>
+      <c r="CS6" s="136"/>
+      <c r="CT6" s="136"/>
     </row>
     <row r="7" spans="1:353" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3"/>
@@ -2281,98 +2281,98 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="151"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="152"/>
-      <c r="L7" s="152"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="152"/>
-      <c r="O7" s="152"/>
-      <c r="P7" s="152"/>
-      <c r="Q7" s="152"/>
-      <c r="R7" s="152"/>
-      <c r="S7" s="152"/>
-      <c r="T7" s="152"/>
-      <c r="U7" s="152"/>
-      <c r="V7" s="152"/>
-      <c r="W7" s="152"/>
-      <c r="X7" s="152"/>
-      <c r="Y7" s="152"/>
-      <c r="Z7" s="152"/>
-      <c r="AA7" s="152"/>
-      <c r="AB7" s="153"/>
-      <c r="AC7" s="154"/>
-      <c r="AD7" s="155"/>
-      <c r="AE7" s="155"/>
-      <c r="AF7" s="155"/>
-      <c r="AG7" s="155"/>
-      <c r="AH7" s="155"/>
-      <c r="AI7" s="155"/>
-      <c r="AJ7" s="155"/>
-      <c r="AK7" s="155"/>
-      <c r="AL7" s="155"/>
-      <c r="AM7" s="155"/>
-      <c r="AN7" s="155"/>
-      <c r="AO7" s="155"/>
-      <c r="AP7" s="155"/>
-      <c r="AQ7" s="155"/>
-      <c r="AR7" s="155"/>
-      <c r="AS7" s="155"/>
-      <c r="AT7" s="155"/>
-      <c r="AU7" s="155"/>
-      <c r="AV7" s="156"/>
-      <c r="AW7" s="157"/>
-      <c r="AX7" s="158"/>
-      <c r="AY7" s="158"/>
-      <c r="AZ7" s="158"/>
-      <c r="BA7" s="158"/>
-      <c r="BB7" s="158"/>
-      <c r="BC7" s="158"/>
-      <c r="BD7" s="158"/>
-      <c r="BE7" s="158"/>
-      <c r="BF7" s="158"/>
-      <c r="BG7" s="158"/>
-      <c r="BH7" s="158"/>
-      <c r="BI7" s="158"/>
-      <c r="BJ7" s="158"/>
-      <c r="BK7" s="158"/>
-      <c r="BL7" s="158"/>
-      <c r="BM7" s="158"/>
-      <c r="BN7" s="158"/>
-      <c r="BO7" s="158"/>
-      <c r="BP7" s="159"/>
-      <c r="BQ7" s="160"/>
-      <c r="BR7" s="161"/>
-      <c r="BS7" s="161"/>
-      <c r="BT7" s="161"/>
-      <c r="BU7" s="161"/>
-      <c r="BV7" s="161"/>
-      <c r="BW7" s="161"/>
-      <c r="BX7" s="161"/>
-      <c r="BY7" s="161"/>
-      <c r="BZ7" s="161"/>
-      <c r="CA7" s="161"/>
-      <c r="CB7" s="161"/>
-      <c r="CC7" s="161"/>
-      <c r="CD7" s="161"/>
-      <c r="CE7" s="161"/>
-      <c r="CF7" s="161"/>
-      <c r="CG7" s="161"/>
-      <c r="CH7" s="161"/>
-      <c r="CI7" s="161"/>
-      <c r="CJ7" s="162"/>
-      <c r="CK7" s="145" t="s">
+      <c r="I7" s="140"/>
+      <c r="J7" s="141"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="141"/>
+      <c r="M7" s="141"/>
+      <c r="N7" s="141"/>
+      <c r="O7" s="141"/>
+      <c r="P7" s="141"/>
+      <c r="Q7" s="141"/>
+      <c r="R7" s="141"/>
+      <c r="S7" s="141"/>
+      <c r="T7" s="141"/>
+      <c r="U7" s="141"/>
+      <c r="V7" s="141"/>
+      <c r="W7" s="141"/>
+      <c r="X7" s="141"/>
+      <c r="Y7" s="141"/>
+      <c r="Z7" s="141"/>
+      <c r="AA7" s="141"/>
+      <c r="AB7" s="142"/>
+      <c r="AC7" s="145"/>
+      <c r="AD7" s="146"/>
+      <c r="AE7" s="146"/>
+      <c r="AF7" s="146"/>
+      <c r="AG7" s="146"/>
+      <c r="AH7" s="146"/>
+      <c r="AI7" s="146"/>
+      <c r="AJ7" s="146"/>
+      <c r="AK7" s="146"/>
+      <c r="AL7" s="146"/>
+      <c r="AM7" s="146"/>
+      <c r="AN7" s="146"/>
+      <c r="AO7" s="146"/>
+      <c r="AP7" s="146"/>
+      <c r="AQ7" s="146"/>
+      <c r="AR7" s="146"/>
+      <c r="AS7" s="146"/>
+      <c r="AT7" s="146"/>
+      <c r="AU7" s="146"/>
+      <c r="AV7" s="147"/>
+      <c r="AW7" s="150"/>
+      <c r="AX7" s="151"/>
+      <c r="AY7" s="151"/>
+      <c r="AZ7" s="151"/>
+      <c r="BA7" s="151"/>
+      <c r="BB7" s="151"/>
+      <c r="BC7" s="151"/>
+      <c r="BD7" s="151"/>
+      <c r="BE7" s="151"/>
+      <c r="BF7" s="151"/>
+      <c r="BG7" s="151"/>
+      <c r="BH7" s="151"/>
+      <c r="BI7" s="151"/>
+      <c r="BJ7" s="151"/>
+      <c r="BK7" s="151"/>
+      <c r="BL7" s="151"/>
+      <c r="BM7" s="151"/>
+      <c r="BN7" s="151"/>
+      <c r="BO7" s="151"/>
+      <c r="BP7" s="152"/>
+      <c r="BQ7" s="155"/>
+      <c r="BR7" s="156"/>
+      <c r="BS7" s="156"/>
+      <c r="BT7" s="156"/>
+      <c r="BU7" s="156"/>
+      <c r="BV7" s="156"/>
+      <c r="BW7" s="156"/>
+      <c r="BX7" s="156"/>
+      <c r="BY7" s="156"/>
+      <c r="BZ7" s="156"/>
+      <c r="CA7" s="156"/>
+      <c r="CB7" s="156"/>
+      <c r="CC7" s="156"/>
+      <c r="CD7" s="156"/>
+      <c r="CE7" s="156"/>
+      <c r="CF7" s="156"/>
+      <c r="CG7" s="156"/>
+      <c r="CH7" s="156"/>
+      <c r="CI7" s="156"/>
+      <c r="CJ7" s="157"/>
+      <c r="CK7" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="CL7" s="146"/>
-      <c r="CM7" s="146"/>
-      <c r="CN7" s="146"/>
-      <c r="CO7" s="146"/>
-      <c r="CP7" s="146"/>
-      <c r="CQ7" s="146"/>
-      <c r="CR7" s="146"/>
-      <c r="CS7" s="146"/>
-      <c r="CT7" s="146"/>
+      <c r="CL7" s="135"/>
+      <c r="CM7" s="135"/>
+      <c r="CN7" s="135"/>
+      <c r="CO7" s="135"/>
+      <c r="CP7" s="135"/>
+      <c r="CQ7" s="135"/>
+      <c r="CR7" s="135"/>
+      <c r="CS7" s="135"/>
+      <c r="CT7" s="135"/>
     </row>
     <row r="8" spans="1:353" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B8" s="63" t="s">
@@ -2396,132 +2396,132 @@
       <c r="H8" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="134" t="s">
+      <c r="I8" s="143" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="135"/>
-      <c r="K8" s="135"/>
-      <c r="L8" s="135"/>
-      <c r="M8" s="135"/>
-      <c r="N8" s="134" t="s">
+      <c r="J8" s="144"/>
+      <c r="K8" s="144"/>
+      <c r="L8" s="144"/>
+      <c r="M8" s="144"/>
+      <c r="N8" s="143" t="s">
         <v>32</v>
       </c>
-      <c r="O8" s="135"/>
-      <c r="P8" s="135"/>
-      <c r="Q8" s="135"/>
-      <c r="R8" s="135"/>
-      <c r="S8" s="134" t="s">
+      <c r="O8" s="144"/>
+      <c r="P8" s="144"/>
+      <c r="Q8" s="144"/>
+      <c r="R8" s="144"/>
+      <c r="S8" s="143" t="s">
         <v>33</v>
       </c>
-      <c r="T8" s="135"/>
-      <c r="U8" s="135"/>
-      <c r="V8" s="135"/>
-      <c r="W8" s="135"/>
-      <c r="X8" s="134" t="s">
+      <c r="T8" s="144"/>
+      <c r="U8" s="144"/>
+      <c r="V8" s="144"/>
+      <c r="W8" s="144"/>
+      <c r="X8" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="Y8" s="135"/>
-      <c r="Z8" s="135"/>
-      <c r="AA8" s="135"/>
-      <c r="AB8" s="135"/>
-      <c r="AC8" s="140" t="s">
+      <c r="Y8" s="144"/>
+      <c r="Z8" s="144"/>
+      <c r="AA8" s="144"/>
+      <c r="AB8" s="144"/>
+      <c r="AC8" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="AD8" s="141"/>
-      <c r="AE8" s="141"/>
-      <c r="AF8" s="141"/>
-      <c r="AG8" s="141"/>
-      <c r="AH8" s="140" t="s">
+      <c r="AD8" s="149"/>
+      <c r="AE8" s="149"/>
+      <c r="AF8" s="149"/>
+      <c r="AG8" s="149"/>
+      <c r="AH8" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="AI8" s="141"/>
-      <c r="AJ8" s="141"/>
-      <c r="AK8" s="141"/>
-      <c r="AL8" s="141"/>
-      <c r="AM8" s="140" t="s">
+      <c r="AI8" s="149"/>
+      <c r="AJ8" s="149"/>
+      <c r="AK8" s="149"/>
+      <c r="AL8" s="149"/>
+      <c r="AM8" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="AN8" s="141"/>
-      <c r="AO8" s="141"/>
-      <c r="AP8" s="141"/>
-      <c r="AQ8" s="141"/>
-      <c r="AR8" s="140" t="s">
+      <c r="AN8" s="149"/>
+      <c r="AO8" s="149"/>
+      <c r="AP8" s="149"/>
+      <c r="AQ8" s="149"/>
+      <c r="AR8" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="AS8" s="141"/>
-      <c r="AT8" s="141"/>
-      <c r="AU8" s="141"/>
-      <c r="AV8" s="141"/>
-      <c r="AW8" s="136" t="s">
+      <c r="AS8" s="149"/>
+      <c r="AT8" s="149"/>
+      <c r="AU8" s="149"/>
+      <c r="AV8" s="149"/>
+      <c r="AW8" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="AX8" s="137"/>
-      <c r="AY8" s="137"/>
-      <c r="AZ8" s="137"/>
-      <c r="BA8" s="137"/>
-      <c r="BB8" s="136" t="s">
+      <c r="AX8" s="154"/>
+      <c r="AY8" s="154"/>
+      <c r="AZ8" s="154"/>
+      <c r="BA8" s="154"/>
+      <c r="BB8" s="153" t="s">
         <v>40</v>
       </c>
-      <c r="BC8" s="137"/>
-      <c r="BD8" s="137"/>
-      <c r="BE8" s="137"/>
-      <c r="BF8" s="137"/>
-      <c r="BG8" s="136" t="s">
+      <c r="BC8" s="154"/>
+      <c r="BD8" s="154"/>
+      <c r="BE8" s="154"/>
+      <c r="BF8" s="154"/>
+      <c r="BG8" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="BH8" s="137"/>
-      <c r="BI8" s="137"/>
-      <c r="BJ8" s="137"/>
-      <c r="BK8" s="137"/>
-      <c r="BL8" s="136" t="s">
+      <c r="BH8" s="154"/>
+      <c r="BI8" s="154"/>
+      <c r="BJ8" s="154"/>
+      <c r="BK8" s="154"/>
+      <c r="BL8" s="153" t="s">
         <v>42</v>
       </c>
-      <c r="BM8" s="137"/>
-      <c r="BN8" s="137"/>
-      <c r="BO8" s="137"/>
-      <c r="BP8" s="137"/>
-      <c r="BQ8" s="138" t="s">
+      <c r="BM8" s="154"/>
+      <c r="BN8" s="154"/>
+      <c r="BO8" s="154"/>
+      <c r="BP8" s="154"/>
+      <c r="BQ8" s="158" t="s">
         <v>48</v>
       </c>
-      <c r="BR8" s="139"/>
-      <c r="BS8" s="139"/>
-      <c r="BT8" s="139"/>
-      <c r="BU8" s="139"/>
-      <c r="BV8" s="138" t="s">
+      <c r="BR8" s="159"/>
+      <c r="BS8" s="159"/>
+      <c r="BT8" s="159"/>
+      <c r="BU8" s="159"/>
+      <c r="BV8" s="158" t="s">
         <v>49</v>
       </c>
-      <c r="BW8" s="139"/>
-      <c r="BX8" s="139"/>
-      <c r="BY8" s="139"/>
-      <c r="BZ8" s="139"/>
-      <c r="CA8" s="138" t="s">
+      <c r="BW8" s="159"/>
+      <c r="BX8" s="159"/>
+      <c r="BY8" s="159"/>
+      <c r="BZ8" s="159"/>
+      <c r="CA8" s="158" t="s">
         <v>50</v>
       </c>
-      <c r="CB8" s="139"/>
-      <c r="CC8" s="139"/>
-      <c r="CD8" s="139"/>
-      <c r="CE8" s="139"/>
-      <c r="CF8" s="131" t="s">
+      <c r="CB8" s="159"/>
+      <c r="CC8" s="159"/>
+      <c r="CD8" s="159"/>
+      <c r="CE8" s="159"/>
+      <c r="CF8" s="160" t="s">
         <v>51</v>
       </c>
-      <c r="CG8" s="132"/>
-      <c r="CH8" s="132"/>
-      <c r="CI8" s="132"/>
-      <c r="CJ8" s="133"/>
-      <c r="CK8" s="142" t="s">
+      <c r="CG8" s="161"/>
+      <c r="CH8" s="161"/>
+      <c r="CI8" s="161"/>
+      <c r="CJ8" s="162"/>
+      <c r="CK8" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="CL8" s="143"/>
-      <c r="CM8" s="143"/>
-      <c r="CN8" s="143"/>
-      <c r="CO8" s="144"/>
-      <c r="CP8" s="142" t="s">
+      <c r="CL8" s="132"/>
+      <c r="CM8" s="132"/>
+      <c r="CN8" s="132"/>
+      <c r="CO8" s="133"/>
+      <c r="CP8" s="131" t="s">
         <v>180</v>
       </c>
-      <c r="CQ8" s="143"/>
-      <c r="CR8" s="143"/>
-      <c r="CS8" s="143"/>
-      <c r="CT8" s="144"/>
+      <c r="CQ8" s="132"/>
+      <c r="CR8" s="132"/>
+      <c r="CS8" s="132"/>
+      <c r="CT8" s="133"/>
     </row>
     <row r="9" spans="1:353" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="64" t="s">
@@ -5931,7 +5931,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="74">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I27" s="86"/>
       <c r="J27" s="87"/>
@@ -6045,7 +6045,7 @@
         <v>5</v>
       </c>
       <c r="H28" s="74">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I28" s="86"/>
       <c r="J28" s="87"/>
@@ -6159,7 +6159,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="74">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I29" s="86"/>
       <c r="J29" s="87"/>
@@ -6635,7 +6635,7 @@
         <v>3</v>
       </c>
       <c r="H31" s="74">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I31" s="86"/>
       <c r="J31" s="87"/>
@@ -6749,7 +6749,7 @@
         <v>4</v>
       </c>
       <c r="H32" s="74">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I32" s="86"/>
       <c r="J32" s="87"/>
@@ -6863,7 +6863,7 @@
         <v>5</v>
       </c>
       <c r="H33" s="74">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I33" s="86"/>
       <c r="J33" s="87"/>
@@ -6977,7 +6977,7 @@
         <v>4</v>
       </c>
       <c r="H34" s="74">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="I34" s="86"/>
       <c r="J34" s="87"/>
@@ -7091,7 +7091,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="74">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I35" s="86"/>
       <c r="J35" s="87"/>
@@ -7795,7 +7795,7 @@
         <v>3</v>
       </c>
       <c r="H39" s="74">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I39" s="86"/>
       <c r="J39" s="87"/>
@@ -7909,7 +7909,7 @@
         <v>5</v>
       </c>
       <c r="H40" s="74">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I40" s="86"/>
       <c r="J40" s="87"/>
@@ -8023,7 +8023,7 @@
         <v>2</v>
       </c>
       <c r="H41" s="74">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I41" s="86"/>
       <c r="J41" s="87"/>
@@ -8137,7 +8137,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="74">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I42" s="86"/>
       <c r="J42" s="87"/>
@@ -8727,7 +8727,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="74">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="I45" s="86"/>
       <c r="J45" s="87"/>
@@ -8841,7 +8841,7 @@
         <v>2</v>
       </c>
       <c r="H46" s="74">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I46" s="86"/>
       <c r="J46" s="87"/>
@@ -14390,6 +14390,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="CF8:CJ8"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="N8:R8"/>
+    <mergeCell ref="BB8:BF8"/>
+    <mergeCell ref="BL8:BP8"/>
+    <mergeCell ref="BQ8:BU8"/>
+    <mergeCell ref="BV8:BZ8"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="AC8:AG8"/>
+    <mergeCell ref="AH8:AL8"/>
+    <mergeCell ref="AR8:AV8"/>
+    <mergeCell ref="AW8:BA8"/>
     <mergeCell ref="CP8:CT8"/>
     <mergeCell ref="CK7:CT7"/>
     <mergeCell ref="I6:X6"/>
@@ -14406,18 +14418,6 @@
     <mergeCell ref="BG8:BK8"/>
     <mergeCell ref="BQ7:CJ7"/>
     <mergeCell ref="CA8:CE8"/>
-    <mergeCell ref="CF8:CJ8"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="N8:R8"/>
-    <mergeCell ref="BB8:BF8"/>
-    <mergeCell ref="BL8:BP8"/>
-    <mergeCell ref="BQ8:BU8"/>
-    <mergeCell ref="BV8:BZ8"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="AC8:AG8"/>
-    <mergeCell ref="AH8:AL8"/>
-    <mergeCell ref="AR8:AV8"/>
-    <mergeCell ref="AW8:BA8"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="H10:H83">
